--- a/tools/importer/reports/import-edc-test-page.report.xlsx
+++ b/tools/importer/reports/import-edc-test-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>dinika-edc-credit-insurance-test.report.json</t>
+  </si>
+  <si>
+    <t>["hero-page","columns-benefits","columns-benefits","columns-benefits","columns-highlight","table-compare","cta-band","form-leadgen","columns-testimonial","accordion-faq","columns-inquiry"]</t>
+  </si>
+  <si>
+    <t>dinika-edc-credit-insurance-test</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>edc-credit-insurance</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:00:31.698Z</t>
+  </si>
+  <si>
+    <t>Trade credit insurance | EDC</t>
+  </si>
+  <si>
+    <t>http://localhost:8123/en/solutions/insurance/credit-insurance.html</t>
+  </si>
+  <si>
     <t>edc-test-page.report.json</t>
   </si>
   <si>
@@ -46,16 +70,13 @@
     <t>edc-test-page</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>2026-07-24T20:18:41.959Z</t>
+    <t>2026-09-30T18:02:48.374Z</t>
   </si>
   <si>
     <t>Export Development Canada (EDC)</t>
   </si>
   <si>
-    <t>https://www.edc.ca/</t>
+    <t>http://localhost:8123/edc-home.html</t>
   </si>
   <si>
     <t>index.report.json</t>
@@ -483,13 +504,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="38" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
@@ -535,27 +556,27 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -587,16 +608,42 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
